--- a/xls/square_16_tri3_19.xlsx
+++ b/xls/square_16_tri3_19.xlsx
@@ -482,13 +482,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-2.153294735740568</v>
+        <v>-2.1532850570453452</v>
       </c>
       <c r="J19">
-        <v>-2.1022497512842677</v>
+        <v>-2.1022495269300863</v>
       </c>
       <c r="K19">
-        <v>0.43904387946271317</v>
+        <v>0.4390584413381779</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-2.5372802580190617</v>
+        <v>-2.5372804020915956</v>
       </c>
       <c r="J20">
-        <v>-2.066889314432754</v>
+        <v>-2.066889402005378</v>
       </c>
       <c r="K20">
-        <v>1.083795448139878</v>
+        <v>1.083795541262518</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-2.367247578832493</v>
+        <v>-2.3672461701624785</v>
       </c>
       <c r="J21">
-        <v>-1.9094880284110163</v>
+        <v>-1.9094879851724773</v>
       </c>
       <c r="K21">
-        <v>1.6545546038422994</v>
+        <v>1.654554452164888</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -587,13 +587,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-2.0483553477432697</v>
+        <v>-2.0483553767972302</v>
       </c>
       <c r="J22">
-        <v>-1.562127558224048</v>
+        <v>-1.5621275628457791</v>
       </c>
       <c r="K22">
-        <v>3.025104691431765</v>
+        <v>3.025104664707738</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-1.6702900633296338</v>
+        <v>-1.6702901876347827</v>
       </c>
       <c r="J23">
-        <v>-1.3320627967633116</v>
+        <v>-1.332062859272153</v>
       </c>
       <c r="K23">
-        <v>3.3690935722113045</v>
+        <v>3.3690935758953358</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.314933366864983</v>
+        <v>-0.31493338632762086</v>
       </c>
       <c r="J24">
-        <v>-0.22576650513857116</v>
+        <v>-0.22576651467505734</v>
       </c>
       <c r="K24">
-        <v>3.7884502392996295</v>
+        <v>3.788450251777354</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -692,13 +692,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>0.0016583830808135672</v>
+        <v>0.001658382956206898</v>
       </c>
       <c r="J25">
-        <v>-0.00037684620713146277</v>
+        <v>-0.0003768462553741535</v>
       </c>
       <c r="K25">
-        <v>3.078170098543899</v>
+        <v>3.078170096583685</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.012738559325098023</v>
+        <v>-0.012738559658931089</v>
       </c>
       <c r="J26">
-        <v>-0.01077302178505985</v>
+        <v>-0.010773022001567626</v>
       </c>
       <c r="K26">
-        <v>3.38242157091741</v>
+        <v>3.382421573475822</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.001541017077075237</v>
+        <v>-0.0015410170595621083</v>
       </c>
       <c r="J27">
-        <v>-0.0010485150260452754</v>
+        <v>-0.0010485150161516229</v>
       </c>
       <c r="K27">
-        <v>2.798304835824536</v>
+        <v>2.7983048347176394</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -797,13 +797,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0028263013283283756</v>
+        <v>-0.0028263013256207238</v>
       </c>
       <c r="J28">
-        <v>-0.0020527024330799022</v>
+        <v>-0.002052702431143951</v>
       </c>
       <c r="K28">
-        <v>2.9636391715858585</v>
+        <v>2.963639171371213</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.00036721523077041076</v>
+        <v>-0.0003672152307983034</v>
       </c>
       <c r="J29">
-        <v>-0.0002535753030892002</v>
+        <v>-0.0002535753031069059</v>
       </c>
       <c r="K29">
-        <v>2.5090610896836254</v>
+        <v>2.509061089693679</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.00064877714546002</v>
+        <v>-0.0006487771456347277</v>
       </c>
       <c r="J30">
-        <v>-0.0004620817708051678</v>
+        <v>-0.00046208177092096203</v>
       </c>
       <c r="K30">
-        <v>2.645363620848643</v>
+        <v>2.6453636210204423</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -902,13 +902,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>8.594053034761338e-7</v>
+        <v>8.59405303861864e-7</v>
       </c>
       <c r="J31">
-        <v>-1.1964102103334869e-5</v>
+        <v>-1.1964102102081209e-5</v>
       </c>
       <c r="K31">
-        <v>2.1970298415306275</v>
+        <v>2.197029841658421</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -937,13 +937,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.0003346050554414579</v>
+        <v>-0.00033460505543253093</v>
       </c>
       <c r="J32">
-        <v>-0.00021521361231966908</v>
+        <v>-0.00021521361231600282</v>
       </c>
       <c r="K32">
-        <v>2.415813827443464</v>
+        <v>2.4158138272928844</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_19.xlsx
+++ b/xls/square_16_tri3_19.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>400</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>289</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>2.5925170977955463</v>
+      </c>
+      <c r="J17">
+        <v>-0.7132418107033056</v>
+      </c>
+      <c r="K17">
+        <v>2.975382383337105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>400</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>289</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>0.7591441613810616</v>
+      </c>
+      <c r="J18">
+        <v>-1.7841873785410634</v>
+      </c>
+      <c r="K18">
+        <v>2.4829784757227435</v>
+      </c>
+    </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
         <v>11</v>
